--- a/Result/profitability/3022.xlsx
+++ b/Result/profitability/3022.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.76</v>
       </c>
       <c r="M2" t="n">
-        <v>1.37125</v>
+        <v>1.455</v>
       </c>
       <c r="N2" t="n">
-        <v>32.99</v>
+        <v>32.03</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>1.73</v>
       </c>
       <c r="M3" t="n">
-        <v>1.37875</v>
+        <v>1.30125</v>
       </c>
       <c r="N3" t="n">
-        <v>32.635</v>
+        <v>31.83625</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.93</v>
       </c>
       <c r="M4" t="n">
-        <v>1.125</v>
+        <v>1.16</v>
       </c>
       <c r="N4" t="n">
-        <v>32.84375</v>
+        <v>31.91125</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>0.8762500000000001</v>
+        <v>1.3775</v>
       </c>
       <c r="N5" t="n">
-        <v>32.4675</v>
+        <v>31.9</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.42</v>
       </c>
       <c r="M6" t="n">
-        <v>1.1375</v>
+        <v>1.16625</v>
       </c>
       <c r="N6" t="n">
-        <v>32.81875</v>
+        <v>32.15875</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.16</v>
       </c>
       <c r="M7" t="n">
-        <v>0.89375</v>
+        <v>0.92125</v>
       </c>
       <c r="N7" t="n">
-        <v>32.8925</v>
+        <v>32.1925</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.04</v>
       </c>
       <c r="M8" t="n">
-        <v>0.75875</v>
+        <v>0.93125</v>
       </c>
       <c r="N8" t="n">
-        <v>32.9625</v>
+        <v>32.90625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>3022</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2489</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1800</v>
+      </c>
+      <c r="E75" t="n">
+        <v>690</v>
+      </c>
+      <c r="F75" t="n">
+        <v>27.7</v>
+      </c>
+      <c r="G75" t="n">
+        <v>228</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.15%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>163</v>
+      </c>
+      <c r="J75" t="n">
+        <v>391</v>
+      </c>
+      <c r="K75" t="n">
+        <v>413</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="M75" t="n">
+        <v>1.56875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>32.375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.4375</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-0.4499999999999993</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.01598579040852577</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.401197604790419</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.540000000000003</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1408188585607941</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
